--- a/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2010/MISSOURI_2010.xlsx
+++ b/2_SQL_database/Data_clean_updated/MCAS/Estados_US/Edos_USA_2010/MISSOURI_2010.xlsx
@@ -1932,7 +1932,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Temosachi</t>
+          <t>Temosachic</t>
         </is>
       </c>
       <c r="C88">
@@ -3012,7 +3012,7 @@
       </c>
       <c r="B148" t="inlineStr">
         <is>
-          <t>Allende</t>
+          <t>San Miguel De Allende</t>
         </is>
       </c>
       <c r="C148">
@@ -8934,7 +8934,7 @@
       </c>
       <c r="B477" t="inlineStr">
         <is>
-          <t>Dr. Arroyo</t>
+          <t>Doctor Arroyo</t>
         </is>
       </c>
       <c r="C477">
@@ -9834,7 +9834,7 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>San Pedro Mixtepec - Distr. 22 -</t>
+          <t>San Pedro Mixtepec -Dto. 22 -</t>
         </is>
       </c>
       <c r="C527">
